--- a/VerveStacks_IND_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_IND_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7579527-A8FB-460C-A06C-DF2C23F11E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EE4FAC4-15FC-4754-96AF-627C38CB1F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1335,13 +1335,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH05,S04aH03,S03aH03,S01aH02,S04aH04,S02aH04,S02aH05,S04aH02,S02aH02,S04aH05,S01aH05,S01aH03,S03aH02,S01aH04,S02aH03,S03aH04</t>
+    <t>S03aH04,S03aH03,S01aH05,S04aH02,S02aH03,S01aH02,S04aH04,S03aH05,S02aH04,S02aH05,S02aH02,S04aH05,S01aH03,S04aH03,S03aH02,S01aH04</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH01,S03aH06,S02aH06,S03aH01,S01aH06,S01aH01,S04aH01,S04aH06</t>
+    <t>S01aH06,S01aH01,S04aH01,S04aH06,S03aH06,S02aH06,S03aH01,S02aH01</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH01,S03aH06,S02aH06,S03aH01,S01aH06,S01aH01,S04aH01,S04aH06</v>
+        <v>S01aH06,S01aH01,S04aH01,S04aH06,S03aH06,S02aH06,S03aH01,S02aH01</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH05,S04aH03,S03aH03,S01aH02,S04aH04,S02aH04,S02aH05,S04aH02,S02aH02,S04aH05,S01aH05,S01aH03,S03aH02,S01aH04,S02aH03,S03aH04</v>
+        <v>S03aH04,S03aH03,S01aH05,S04aH02,S02aH03,S01aH02,S04aH04,S03aH05,S02aH04,S02aH05,S02aH02,S04aH05,S01aH03,S04aH03,S03aH02,S01aH04</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2064,7 +2064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{629CE303-B95B-473B-9E9B-31F0A541BDBF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFE34AF1-E9E2-4DCF-A8B1-13BE1476DBBD}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2170,7 +2170,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E44B2319-4161-4031-9099-85631D0F9916}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39B54AC3-05CA-44C1-A42E-3DE2FDF6C99C}">
   <dimension ref="B9:O1882"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -54648,7 +54648,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309CB477-E855-4AB8-A227-614B5E092BB1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC76FA6B-47B5-4174-AC74-C4FF640F7497}">
   <dimension ref="B9:DH179"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -83694,7 +83694,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B8E1E4D-1321-44C9-A85B-C66688A56D17}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ADF82B5-2E30-4AB0-908C-4399CB4C48C2}">
   <dimension ref="B9:E34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -84060,7 +84060,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78AEE14A-9CF4-4962-AABA-90638F6814B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7C1EA53-8BFD-44FD-AEC4-9ACA3D154DE2}">
   <dimension ref="B9:D58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -84615,7 +84615,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD6BD118-AA77-433E-9856-AD483B32B122}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97B73106-62FD-44A8-8D29-DC7E97DAF0EC}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -84906,7 +84906,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C77FAE07-F366-4A3B-906D-BB8B56956B3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B26B50E-1BD2-4A3A-9DBA-3D16E201DD03}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -84938,7 +84938,7 @@
         <v>37</v>
       </c>
       <c r="D11">
-        <v>0.26990000000000003</v>
+        <v>0.26989999999999997</v>
       </c>
       <c r="E11" t="s">
         <v>439</v>
@@ -85022,7 +85022,7 @@
         <v>43</v>
       </c>
       <c r="D17">
-        <v>0.56513333333333338</v>
+        <v>0.56513333333333327</v>
       </c>
       <c r="E17" t="s">
         <v>439</v>
@@ -85134,7 +85134,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.5820333333333334</v>
+        <v>0.58203333333333329</v>
       </c>
       <c r="E25" t="s">
         <v>439</v>
@@ -85162,7 +85162,7 @@
         <v>37</v>
       </c>
       <c r="D27">
-        <v>0.21880000000000002</v>
+        <v>0.21879999999999999</v>
       </c>
       <c r="E27" t="s">
         <v>439</v>
@@ -85442,7 +85442,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.18899999999999997</v>
+        <v>0.18900000000000003</v>
       </c>
       <c r="E47" t="s">
         <v>439</v>
@@ -85582,7 +85582,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.43829999999999997</v>
+        <v>0.43830000000000008</v>
       </c>
       <c r="E57" t="s">
         <v>439</v>
@@ -85610,7 +85610,7 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>0.23069999999999999</v>
+        <v>0.23070000000000002</v>
       </c>
       <c r="E59" t="s">
         <v>439</v>
@@ -85666,7 +85666,7 @@
         <v>37</v>
       </c>
       <c r="D63">
-        <v>0.24303333333333335</v>
+        <v>0.24303333333333332</v>
       </c>
       <c r="E63" t="s">
         <v>439</v>
@@ -85722,7 +85722,7 @@
         <v>37</v>
       </c>
       <c r="D67">
-        <v>0.23089999999999999</v>
+        <v>0.23090000000000002</v>
       </c>
       <c r="E67" t="s">
         <v>439</v>
@@ -85946,7 +85946,7 @@
         <v>37</v>
       </c>
       <c r="D83">
-        <v>0.26106666666666667</v>
+        <v>0.26106666666666661</v>
       </c>
       <c r="E83" t="s">
         <v>439</v>
@@ -86002,7 +86002,7 @@
         <v>37</v>
       </c>
       <c r="D87">
-        <v>0.2869666666666667</v>
+        <v>0.28696666666666665</v>
       </c>
       <c r="E87" t="s">
         <v>439</v>
@@ -86030,7 +86030,7 @@
         <v>43</v>
       </c>
       <c r="D89">
-        <v>0.60863333333333336</v>
+        <v>0.60863333333333325</v>
       </c>
       <c r="E89" t="s">
         <v>439</v>
@@ -86058,7 +86058,7 @@
         <v>37</v>
       </c>
       <c r="D91">
-        <v>0.28143333333333337</v>
+        <v>0.28143333333333331</v>
       </c>
       <c r="E91" t="s">
         <v>439</v>
@@ -86114,7 +86114,7 @@
         <v>37</v>
       </c>
       <c r="D95">
-        <v>0.24973333333333333</v>
+        <v>0.24973333333333336</v>
       </c>
       <c r="E95" t="s">
         <v>439</v>
@@ -86198,7 +86198,7 @@
         <v>43</v>
       </c>
       <c r="D101">
-        <v>0.5054333333333334</v>
+        <v>0.50543333333333329</v>
       </c>
       <c r="E101" t="s">
         <v>439</v>
@@ -86394,7 +86394,7 @@
         <v>37</v>
       </c>
       <c r="D115">
-        <v>0.22640000000000002</v>
+        <v>0.22639999999999996</v>
       </c>
       <c r="E115" t="s">
         <v>439</v>
@@ -86534,7 +86534,7 @@
         <v>43</v>
       </c>
       <c r="D125">
-        <v>0.49769999999999998</v>
+        <v>0.49770000000000003</v>
       </c>
       <c r="E125" t="s">
         <v>439</v>
